--- a/Australia/data_raw/5232035.xlsx
+++ b/Australia/data_raw/5232035.xlsx
@@ -17,104 +17,104 @@
     <sheet name="Enquiries" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="A83722644R">Data1!$AC$1:$AC$10,Data1!$AC$11:$AC$159</definedName>
-    <definedName name="A83722644R_Data">Data1!$AC$11:$AC$159</definedName>
-    <definedName name="A83722644R_Latest">Data1!$AC$159</definedName>
-    <definedName name="A83722646V">Data1!$K$1:$K$10,Data1!$K$11:$K$159</definedName>
-    <definedName name="A83722646V_Data">Data1!$K$11:$K$159</definedName>
-    <definedName name="A83722646V_Latest">Data1!$K$159</definedName>
-    <definedName name="A83722647W">Data1!$I$1:$I$10,Data1!$I$11:$I$159</definedName>
-    <definedName name="A83722647W_Data">Data1!$I$11:$I$159</definedName>
-    <definedName name="A83722647W_Latest">Data1!$I$159</definedName>
-    <definedName name="A83722648X">Data1!$AE$1:$AE$10,Data1!$AE$11:$AE$159</definedName>
-    <definedName name="A83722648X_Data">Data1!$AE$11:$AE$159</definedName>
-    <definedName name="A83722648X_Latest">Data1!$AE$159</definedName>
-    <definedName name="A83722651L">Data1!$G$1:$G$10,Data1!$G$11:$G$159</definedName>
-    <definedName name="A83722651L_Data">Data1!$G$11:$G$159</definedName>
-    <definedName name="A83722651L_Latest">Data1!$G$159</definedName>
-    <definedName name="A83722652R">Data1!$AD$1:$AD$10,Data1!$AD$11:$AD$159</definedName>
-    <definedName name="A83722652R_Data">Data1!$AD$11:$AD$159</definedName>
-    <definedName name="A83722652R_Latest">Data1!$AD$159</definedName>
-    <definedName name="A83722653T">Data1!$H$1:$H$10,Data1!$H$11:$H$159</definedName>
-    <definedName name="A83722653T_Data">Data1!$H$11:$H$159</definedName>
-    <definedName name="A83722653T_Latest">Data1!$H$159</definedName>
-    <definedName name="A83722654V">Data1!$C$1:$C$10,Data1!$C$11:$C$159</definedName>
-    <definedName name="A83722654V_Data">Data1!$C$11:$C$159</definedName>
-    <definedName name="A83722654V_Latest">Data1!$C$159</definedName>
-    <definedName name="A83722657A">Data1!$S$1:$S$10,Data1!$S$11:$S$159</definedName>
-    <definedName name="A83722657A_Data">Data1!$S$11:$S$159</definedName>
-    <definedName name="A83722657A_Latest">Data1!$S$159</definedName>
-    <definedName name="A83722659F">Data1!$Z$1:$Z$10,Data1!$Z$11:$Z$159</definedName>
-    <definedName name="A83722659F_Data">Data1!$Z$11:$Z$159</definedName>
-    <definedName name="A83722659F_Latest">Data1!$Z$159</definedName>
-    <definedName name="A83722663W">Data1!$D$1:$D$10,Data1!$D$11:$D$159</definedName>
-    <definedName name="A83722663W_Data">Data1!$D$11:$D$159</definedName>
-    <definedName name="A83722663W_Latest">Data1!$D$159</definedName>
-    <definedName name="A83722664X">Data1!$Q$1:$Q$10,Data1!$Q$11:$Q$159</definedName>
-    <definedName name="A83722664X_Data">Data1!$Q$11:$Q$159</definedName>
-    <definedName name="A83722664X_Latest">Data1!$Q$159</definedName>
-    <definedName name="A83722665A">Data1!$V$1:$V$10,Data1!$V$11:$V$159</definedName>
-    <definedName name="A83722665A_Data">Data1!$V$11:$V$159</definedName>
-    <definedName name="A83722665A_Latest">Data1!$V$159</definedName>
-    <definedName name="A83722666C">Data1!$AG$1:$AG$10,Data1!$AG$11:$AG$159</definedName>
-    <definedName name="A83722666C_Data">Data1!$AG$11:$AG$159</definedName>
-    <definedName name="A83722666C_Latest">Data1!$AG$159</definedName>
-    <definedName name="A83722667F">Data1!$J$1:$J$10,Data1!$J$11:$J$159</definedName>
-    <definedName name="A83722667F_Data">Data1!$J$11:$J$159</definedName>
-    <definedName name="A83722667F_Latest">Data1!$J$159</definedName>
-    <definedName name="A83722668J">Data1!$M$1:$M$10,Data1!$M$11:$M$159</definedName>
-    <definedName name="A83722668J_Data">Data1!$M$11:$M$159</definedName>
-    <definedName name="A83722668J_Latest">Data1!$M$159</definedName>
-    <definedName name="A83722669K">Data1!$W$1:$W$10,Data1!$W$11:$W$159</definedName>
-    <definedName name="A83722669K_Data">Data1!$W$11:$W$159</definedName>
-    <definedName name="A83722669K_Latest">Data1!$W$159</definedName>
-    <definedName name="A83722670V">Data1!$AA$1:$AA$10,Data1!$AA$11:$AA$159</definedName>
-    <definedName name="A83722670V_Data">Data1!$AA$11:$AA$159</definedName>
-    <definedName name="A83722670V_Latest">Data1!$AA$159</definedName>
-    <definedName name="A83722673A">Data1!$P$1:$P$10,Data1!$P$11:$P$159</definedName>
-    <definedName name="A83722673A_Data">Data1!$P$11:$P$159</definedName>
-    <definedName name="A83722673A_Latest">Data1!$P$159</definedName>
-    <definedName name="A83722675F">Data1!$U$1:$U$10,Data1!$U$11:$U$159</definedName>
-    <definedName name="A83722675F_Data">Data1!$U$11:$U$159</definedName>
-    <definedName name="A83722675F_Latest">Data1!$U$159</definedName>
-    <definedName name="A83722676J">Data1!$AB$1:$AB$10,Data1!$AB$11:$AB$159</definedName>
-    <definedName name="A83722676J_Data">Data1!$AB$11:$AB$159</definedName>
-    <definedName name="A83722676J_Latest">Data1!$AB$159</definedName>
-    <definedName name="A83722678L">Data1!$L$1:$L$10,Data1!$L$11:$L$159</definedName>
-    <definedName name="A83722678L_Data">Data1!$L$11:$L$159</definedName>
-    <definedName name="A83722678L_Latest">Data1!$L$159</definedName>
-    <definedName name="A83722679R">Data1!$O$1:$O$10,Data1!$O$11:$O$159</definedName>
-    <definedName name="A83722679R_Data">Data1!$O$11:$O$159</definedName>
-    <definedName name="A83722679R_Latest">Data1!$O$159</definedName>
-    <definedName name="A83722680X">Data1!$T$1:$T$10,Data1!$T$11:$T$159</definedName>
-    <definedName name="A83722680X_Data">Data1!$T$11:$T$159</definedName>
-    <definedName name="A83722680X_Latest">Data1!$T$159</definedName>
-    <definedName name="A83722685K">Data1!$B$1:$B$10,Data1!$B$11:$B$159</definedName>
-    <definedName name="A83722685K_Data">Data1!$B$11:$B$159</definedName>
-    <definedName name="A83722685K_Latest">Data1!$B$159</definedName>
-    <definedName name="A83722686L">Data1!$F$1:$F$10,Data1!$F$11:$F$159</definedName>
-    <definedName name="A83722686L_Data">Data1!$F$11:$F$159</definedName>
-    <definedName name="A83722686L_Latest">Data1!$F$159</definedName>
-    <definedName name="A83722687R">Data1!$R$1:$R$10,Data1!$R$11:$R$159</definedName>
-    <definedName name="A83722687R_Data">Data1!$R$11:$R$159</definedName>
-    <definedName name="A83722687R_Latest">Data1!$R$159</definedName>
-    <definedName name="A83722688T">Data1!$N$1:$N$10,Data1!$N$11:$N$159</definedName>
-    <definedName name="A83722688T_Data">Data1!$N$11:$N$159</definedName>
-    <definedName name="A83722688T_Latest">Data1!$N$159</definedName>
-    <definedName name="A83722691F">Data1!$E$1:$E$10,Data1!$E$11:$E$159</definedName>
-    <definedName name="A83722691F_Data">Data1!$E$11:$E$159</definedName>
-    <definedName name="A83722691F_Latest">Data1!$E$159</definedName>
-    <definedName name="A83728303A">Data1!$X$1:$X$10,Data1!$X$11:$X$159</definedName>
-    <definedName name="A83728303A_Data">Data1!$X$11:$X$159</definedName>
-    <definedName name="A83728303A_Latest">Data1!$X$159</definedName>
-    <definedName name="A83728304C">Data1!$Y$1:$Y$10,Data1!$Y$11:$Y$159</definedName>
-    <definedName name="A83728304C_Data">Data1!$Y$11:$Y$159</definedName>
-    <definedName name="A83728304C_Latest">Data1!$Y$159</definedName>
-    <definedName name="A83728305F">Data1!$AF$1:$AF$10,Data1!$AF$11:$AF$159</definedName>
-    <definedName name="A83728305F_Data">Data1!$AF$11:$AF$159</definedName>
-    <definedName name="A83728305F_Latest">Data1!$AF$159</definedName>
-    <definedName name="Date_Range">Data1!$A$2:$A$10,Data1!$A$11:$A$159</definedName>
-    <definedName name="Date_Range_Data">Data1!$A$11:$A$159</definedName>
+    <definedName name="A83722644R">Data1!$AC$1:$AC$10,Data1!$AC$11:$AC$161</definedName>
+    <definedName name="A83722644R_Data">Data1!$AC$11:$AC$161</definedName>
+    <definedName name="A83722644R_Latest">Data1!$AC$161</definedName>
+    <definedName name="A83722646V">Data1!$K$1:$K$10,Data1!$K$11:$K$161</definedName>
+    <definedName name="A83722646V_Data">Data1!$K$11:$K$161</definedName>
+    <definedName name="A83722646V_Latest">Data1!$K$161</definedName>
+    <definedName name="A83722647W">Data1!$I$1:$I$10,Data1!$I$11:$I$161</definedName>
+    <definedName name="A83722647W_Data">Data1!$I$11:$I$161</definedName>
+    <definedName name="A83722647W_Latest">Data1!$I$161</definedName>
+    <definedName name="A83722648X">Data1!$AE$1:$AE$10,Data1!$AE$11:$AE$161</definedName>
+    <definedName name="A83722648X_Data">Data1!$AE$11:$AE$161</definedName>
+    <definedName name="A83722648X_Latest">Data1!$AE$161</definedName>
+    <definedName name="A83722651L">Data1!$G$1:$G$10,Data1!$G$11:$G$161</definedName>
+    <definedName name="A83722651L_Data">Data1!$G$11:$G$161</definedName>
+    <definedName name="A83722651L_Latest">Data1!$G$161</definedName>
+    <definedName name="A83722652R">Data1!$AD$1:$AD$10,Data1!$AD$11:$AD$161</definedName>
+    <definedName name="A83722652R_Data">Data1!$AD$11:$AD$161</definedName>
+    <definedName name="A83722652R_Latest">Data1!$AD$161</definedName>
+    <definedName name="A83722653T">Data1!$H$1:$H$10,Data1!$H$11:$H$161</definedName>
+    <definedName name="A83722653T_Data">Data1!$H$11:$H$161</definedName>
+    <definedName name="A83722653T_Latest">Data1!$H$161</definedName>
+    <definedName name="A83722654V">Data1!$C$1:$C$10,Data1!$C$11:$C$161</definedName>
+    <definedName name="A83722654V_Data">Data1!$C$11:$C$161</definedName>
+    <definedName name="A83722654V_Latest">Data1!$C$161</definedName>
+    <definedName name="A83722657A">Data1!$S$1:$S$10,Data1!$S$11:$S$161</definedName>
+    <definedName name="A83722657A_Data">Data1!$S$11:$S$161</definedName>
+    <definedName name="A83722657A_Latest">Data1!$S$161</definedName>
+    <definedName name="A83722659F">Data1!$Z$1:$Z$10,Data1!$Z$11:$Z$161</definedName>
+    <definedName name="A83722659F_Data">Data1!$Z$11:$Z$161</definedName>
+    <definedName name="A83722659F_Latest">Data1!$Z$161</definedName>
+    <definedName name="A83722663W">Data1!$D$1:$D$10,Data1!$D$11:$D$161</definedName>
+    <definedName name="A83722663W_Data">Data1!$D$11:$D$161</definedName>
+    <definedName name="A83722663W_Latest">Data1!$D$161</definedName>
+    <definedName name="A83722664X">Data1!$Q$1:$Q$10,Data1!$Q$11:$Q$161</definedName>
+    <definedName name="A83722664X_Data">Data1!$Q$11:$Q$161</definedName>
+    <definedName name="A83722664X_Latest">Data1!$Q$161</definedName>
+    <definedName name="A83722665A">Data1!$V$1:$V$10,Data1!$V$11:$V$161</definedName>
+    <definedName name="A83722665A_Data">Data1!$V$11:$V$161</definedName>
+    <definedName name="A83722665A_Latest">Data1!$V$161</definedName>
+    <definedName name="A83722666C">Data1!$AG$1:$AG$10,Data1!$AG$11:$AG$161</definedName>
+    <definedName name="A83722666C_Data">Data1!$AG$11:$AG$161</definedName>
+    <definedName name="A83722666C_Latest">Data1!$AG$161</definedName>
+    <definedName name="A83722667F">Data1!$J$1:$J$10,Data1!$J$11:$J$161</definedName>
+    <definedName name="A83722667F_Data">Data1!$J$11:$J$161</definedName>
+    <definedName name="A83722667F_Latest">Data1!$J$161</definedName>
+    <definedName name="A83722668J">Data1!$M$1:$M$10,Data1!$M$11:$M$161</definedName>
+    <definedName name="A83722668J_Data">Data1!$M$11:$M$161</definedName>
+    <definedName name="A83722668J_Latest">Data1!$M$161</definedName>
+    <definedName name="A83722669K">Data1!$W$1:$W$10,Data1!$W$11:$W$161</definedName>
+    <definedName name="A83722669K_Data">Data1!$W$11:$W$161</definedName>
+    <definedName name="A83722669K_Latest">Data1!$W$161</definedName>
+    <definedName name="A83722670V">Data1!$AA$1:$AA$10,Data1!$AA$11:$AA$161</definedName>
+    <definedName name="A83722670V_Data">Data1!$AA$11:$AA$161</definedName>
+    <definedName name="A83722670V_Latest">Data1!$AA$161</definedName>
+    <definedName name="A83722673A">Data1!$P$1:$P$10,Data1!$P$11:$P$161</definedName>
+    <definedName name="A83722673A_Data">Data1!$P$11:$P$161</definedName>
+    <definedName name="A83722673A_Latest">Data1!$P$161</definedName>
+    <definedName name="A83722675F">Data1!$U$1:$U$10,Data1!$U$11:$U$161</definedName>
+    <definedName name="A83722675F_Data">Data1!$U$11:$U$161</definedName>
+    <definedName name="A83722675F_Latest">Data1!$U$161</definedName>
+    <definedName name="A83722676J">Data1!$AB$1:$AB$10,Data1!$AB$11:$AB$161</definedName>
+    <definedName name="A83722676J_Data">Data1!$AB$11:$AB$161</definedName>
+    <definedName name="A83722676J_Latest">Data1!$AB$161</definedName>
+    <definedName name="A83722678L">Data1!$L$1:$L$10,Data1!$L$11:$L$161</definedName>
+    <definedName name="A83722678L_Data">Data1!$L$11:$L$161</definedName>
+    <definedName name="A83722678L_Latest">Data1!$L$161</definedName>
+    <definedName name="A83722679R">Data1!$O$1:$O$10,Data1!$O$11:$O$161</definedName>
+    <definedName name="A83722679R_Data">Data1!$O$11:$O$161</definedName>
+    <definedName name="A83722679R_Latest">Data1!$O$161</definedName>
+    <definedName name="A83722680X">Data1!$T$1:$T$10,Data1!$T$11:$T$161</definedName>
+    <definedName name="A83722680X_Data">Data1!$T$11:$T$161</definedName>
+    <definedName name="A83722680X_Latest">Data1!$T$161</definedName>
+    <definedName name="A83722685K">Data1!$B$1:$B$10,Data1!$B$11:$B$161</definedName>
+    <definedName name="A83722685K_Data">Data1!$B$11:$B$161</definedName>
+    <definedName name="A83722685K_Latest">Data1!$B$161</definedName>
+    <definedName name="A83722686L">Data1!$F$1:$F$10,Data1!$F$11:$F$161</definedName>
+    <definedName name="A83722686L_Data">Data1!$F$11:$F$161</definedName>
+    <definedName name="A83722686L_Latest">Data1!$F$161</definedName>
+    <definedName name="A83722687R">Data1!$R$1:$R$10,Data1!$R$11:$R$161</definedName>
+    <definedName name="A83722687R_Data">Data1!$R$11:$R$161</definedName>
+    <definedName name="A83722687R_Latest">Data1!$R$161</definedName>
+    <definedName name="A83722688T">Data1!$N$1:$N$10,Data1!$N$11:$N$161</definedName>
+    <definedName name="A83722688T_Data">Data1!$N$11:$N$161</definedName>
+    <definedName name="A83722688T_Latest">Data1!$N$161</definedName>
+    <definedName name="A83722691F">Data1!$E$1:$E$10,Data1!$E$11:$E$161</definedName>
+    <definedName name="A83722691F_Data">Data1!$E$11:$E$161</definedName>
+    <definedName name="A83722691F_Latest">Data1!$E$161</definedName>
+    <definedName name="A83728303A">Data1!$X$1:$X$10,Data1!$X$11:$X$161</definedName>
+    <definedName name="A83728303A_Data">Data1!$X$11:$X$161</definedName>
+    <definedName name="A83728303A_Latest">Data1!$X$161</definedName>
+    <definedName name="A83728304C">Data1!$Y$1:$Y$10,Data1!$Y$11:$Y$161</definedName>
+    <definedName name="A83728304C_Data">Data1!$Y$11:$Y$161</definedName>
+    <definedName name="A83728304C_Latest">Data1!$Y$161</definedName>
+    <definedName name="A83728305F">Data1!$AF$1:$AF$10,Data1!$AF$11:$AF$161</definedName>
+    <definedName name="A83728305F_Data">Data1!$AF$11:$AF$161</definedName>
+    <definedName name="A83728305F_Latest">Data1!$AF$161</definedName>
+    <definedName name="Date_Range">Data1!$A$2:$A$10,Data1!$A$11:$A$161</definedName>
+    <definedName name="Date_Range_Data">Data1!$A$11:$A$161</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -541,7 +541,7 @@
     <t>Freq.</t>
   </si>
   <si>
-    <t>© Commonwealth of Australia  2025</t>
+    <t>© Commonwealth of Australia  2026</t>
   </si>
 </sst>
 </file>
@@ -1222,10 +1222,10 @@
         <v>32387</v>
       </c>
       <c r="G12" s="9">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="H12" s="10">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I12" s="10" t="s">
         <v>41</v>
@@ -1254,10 +1254,10 @@
         <v>32387</v>
       </c>
       <c r="G13" s="9">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="H13" s="10">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>41</v>
@@ -1286,10 +1286,10 @@
         <v>32387</v>
       </c>
       <c r="G14" s="9">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="H14" s="10">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I14" s="10" t="s">
         <v>41</v>
@@ -1318,10 +1318,10 @@
         <v>32387</v>
       </c>
       <c r="G15" s="9">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="H15" s="10">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I15" s="10" t="s">
         <v>41</v>
@@ -1350,10 +1350,10 @@
         <v>32387</v>
       </c>
       <c r="G16" s="9">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="H16" s="10">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I16" s="10" t="s">
         <v>41</v>
@@ -1382,10 +1382,10 @@
         <v>32387</v>
       </c>
       <c r="G17" s="9">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="H17" s="10">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I17" s="10" t="s">
         <v>41</v>
@@ -1414,10 +1414,10 @@
         <v>32387</v>
       </c>
       <c r="G18" s="9">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="H18" s="10">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I18" s="10" t="s">
         <v>41</v>
@@ -1446,10 +1446,10 @@
         <v>32387</v>
       </c>
       <c r="G19" s="9">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="H19" s="10">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>41</v>
@@ -1478,10 +1478,10 @@
         <v>32387</v>
       </c>
       <c r="G20" s="9">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="H20" s="10">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I20" s="10" t="s">
         <v>41</v>
@@ -1510,10 +1510,10 @@
         <v>32387</v>
       </c>
       <c r="G21" s="9">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="H21" s="10">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I21" s="10" t="s">
         <v>41</v>
@@ -1542,10 +1542,10 @@
         <v>32387</v>
       </c>
       <c r="G22" s="9">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="H22" s="10">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>41</v>
@@ -1574,10 +1574,10 @@
         <v>32387</v>
       </c>
       <c r="G23" s="9">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="H23" s="10">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I23" s="10" t="s">
         <v>41</v>
@@ -1606,10 +1606,10 @@
         <v>32387</v>
       </c>
       <c r="G24" s="9">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="H24" s="10">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I24" s="10" t="s">
         <v>41</v>
@@ -1638,10 +1638,10 @@
         <v>32387</v>
       </c>
       <c r="G25" s="9">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="H25" s="10">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I25" s="10" t="s">
         <v>41</v>
@@ -1670,10 +1670,10 @@
         <v>32387</v>
       </c>
       <c r="G26" s="9">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="H26" s="10">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I26" s="10" t="s">
         <v>41</v>
@@ -1702,10 +1702,10 @@
         <v>32387</v>
       </c>
       <c r="G27" s="9">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="H27" s="10">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I27" s="10" t="s">
         <v>41</v>
@@ -1734,10 +1734,10 @@
         <v>32387</v>
       </c>
       <c r="G28" s="9">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="H28" s="10">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I28" s="10" t="s">
         <v>41</v>
@@ -1766,10 +1766,10 @@
         <v>32387</v>
       </c>
       <c r="G29" s="9">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="H29" s="10">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I29" s="10" t="s">
         <v>41</v>
@@ -1798,10 +1798,10 @@
         <v>32387</v>
       </c>
       <c r="G30" s="9">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="H30" s="10">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I30" s="10" t="s">
         <v>41</v>
@@ -1830,10 +1830,10 @@
         <v>32387</v>
       </c>
       <c r="G31" s="9">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="H31" s="10">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I31" s="10" t="s">
         <v>41</v>
@@ -1862,10 +1862,10 @@
         <v>32387</v>
       </c>
       <c r="G32" s="9">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="H32" s="10">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I32" s="10" t="s">
         <v>41</v>
@@ -1894,10 +1894,10 @@
         <v>32387</v>
       </c>
       <c r="G33" s="9">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="H33" s="10">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I33" s="10" t="s">
         <v>41</v>
@@ -1926,10 +1926,10 @@
         <v>32387</v>
       </c>
       <c r="G34" s="9">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="H34" s="10">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I34" s="10" t="s">
         <v>41</v>
@@ -1958,10 +1958,10 @@
         <v>32387</v>
       </c>
       <c r="G35" s="9">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="H35" s="10">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I35" s="10" t="s">
         <v>41</v>
@@ -1990,10 +1990,10 @@
         <v>32387</v>
       </c>
       <c r="G36" s="9">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="H36" s="10">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I36" s="10" t="s">
         <v>41</v>
@@ -2022,10 +2022,10 @@
         <v>32387</v>
       </c>
       <c r="G37" s="9">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="H37" s="10">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I37" s="10" t="s">
         <v>41</v>
@@ -2054,10 +2054,10 @@
         <v>32387</v>
       </c>
       <c r="G38" s="9">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="H38" s="10">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I38" s="10" t="s">
         <v>41</v>
@@ -2086,10 +2086,10 @@
         <v>32387</v>
       </c>
       <c r="G39" s="9">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="H39" s="10">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I39" s="10" t="s">
         <v>41</v>
@@ -2118,10 +2118,10 @@
         <v>32387</v>
       </c>
       <c r="G40" s="9">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="H40" s="10">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I40" s="10" t="s">
         <v>41</v>
@@ -2150,10 +2150,10 @@
         <v>32387</v>
       </c>
       <c r="G41" s="9">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="H41" s="10">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I41" s="10" t="s">
         <v>41</v>
@@ -2182,10 +2182,10 @@
         <v>32387</v>
       </c>
       <c r="G42" s="9">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="H42" s="10">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I42" s="10" t="s">
         <v>41</v>
@@ -2214,10 +2214,10 @@
         <v>32387</v>
       </c>
       <c r="G43" s="9">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="H43" s="10">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I43" s="10" t="s">
         <v>41</v>
@@ -2284,7 +2284,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG159"/>
+  <dimension ref="A1:AG161"/>
   <sheetFormatPr defaultColWidth="14.7109375" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="14.7109375" style="1"/>
@@ -2999,100 +2999,100 @@
         <v>38</v>
       </c>
       <c r="B8" s="6">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="C8" s="6">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="D8" s="6">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="E8" s="6">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="F8" s="6">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="G8" s="6">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="H8" s="6">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="I8" s="6">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="J8" s="6">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="K8" s="6">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="L8" s="6">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="M8" s="6">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="N8" s="6">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="O8" s="6">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="P8" s="6">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="Q8" s="6">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="R8" s="6">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="S8" s="6">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="T8" s="6">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="U8" s="6">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="V8" s="6">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="W8" s="6">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="X8" s="6">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="Y8" s="6">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="Z8" s="6">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="AA8" s="6">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="AB8" s="6">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="AC8" s="6">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="AD8" s="6">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="AE8" s="6">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="AF8" s="6">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="AG8" s="6">
-        <v>45901</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.2">
@@ -3100,100 +3100,100 @@
         <v>39</v>
       </c>
       <c r="B9" s="1">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C9" s="1">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D9" s="1">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E9" s="1">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F9" s="1">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G9" s="1">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H9" s="1">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I9" s="1">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J9" s="1">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K9" s="1">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="L9" s="1">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="M9" s="1">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="N9" s="1">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O9" s="1">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="P9" s="1">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Q9" s="1">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="R9" s="1">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="S9" s="1">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="T9" s="1">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="U9" s="1">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="V9" s="1">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="W9" s="1">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="X9" s="1">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Y9" s="1">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Z9" s="1">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AA9" s="1">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AB9" s="1">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AC9" s="1">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AD9" s="1">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AE9" s="1">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AF9" s="1">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AG9" s="1">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.2">
@@ -17543,7 +17543,7 @@
         <v>45261</v>
       </c>
       <c r="B152" s="8">
-        <v>18972.3</v>
+        <v>18966.400000000001</v>
       </c>
       <c r="C152" s="8">
         <v>11706</v>
@@ -17594,7 +17594,7 @@
         <v>0.1</v>
       </c>
       <c r="S152" s="8">
-        <v>7266.3</v>
+        <v>7260.3</v>
       </c>
       <c r="T152" s="8">
         <v>1688.1</v>
@@ -17609,28 +17609,28 @@
         <v>1402</v>
       </c>
       <c r="X152" s="8">
-        <v>3781.4</v>
+        <v>3775.4</v>
       </c>
       <c r="Y152" s="8">
         <v>227.3</v>
       </c>
       <c r="Z152" s="8">
-        <v>159.19999999999999</v>
+        <v>159.30000000000001</v>
       </c>
       <c r="AA152" s="8">
-        <v>3037.7</v>
+        <v>3040.7</v>
       </c>
       <c r="AB152" s="8">
         <v>4.2</v>
       </c>
       <c r="AC152" s="8">
-        <v>2869.1</v>
+        <v>2872</v>
       </c>
       <c r="AD152" s="8">
-        <v>164.4</v>
+        <v>164.6</v>
       </c>
       <c r="AE152" s="8">
-        <v>15934.6</v>
+        <v>15925.6</v>
       </c>
       <c r="AF152" s="8">
         <v>10149.700000000001</v>
@@ -17644,7 +17644,7 @@
         <v>45352</v>
       </c>
       <c r="B153" s="8">
-        <v>19398.3</v>
+        <v>19389.8</v>
       </c>
       <c r="C153" s="8">
         <v>11891.7</v>
@@ -17695,7 +17695,7 @@
         <v>0.2</v>
       </c>
       <c r="S153" s="8">
-        <v>7506.7</v>
+        <v>7498.1</v>
       </c>
       <c r="T153" s="8">
         <v>1720.1</v>
@@ -17710,28 +17710,28 @@
         <v>1459.6</v>
       </c>
       <c r="X153" s="8">
-        <v>3926.9</v>
+        <v>3919.9</v>
       </c>
       <c r="Y153" s="8">
-        <v>232</v>
+        <v>232.1</v>
       </c>
       <c r="Z153" s="8">
-        <v>160.1</v>
+        <v>158.4</v>
       </c>
       <c r="AA153" s="8">
-        <v>3082.1</v>
+        <v>3087.3</v>
       </c>
       <c r="AB153" s="8">
         <v>4</v>
       </c>
       <c r="AC153" s="8">
-        <v>2911.3</v>
+        <v>2915</v>
       </c>
       <c r="AD153" s="8">
-        <v>166.8</v>
+        <v>168.2</v>
       </c>
       <c r="AE153" s="8">
-        <v>16316.2</v>
+        <v>16302.5</v>
       </c>
       <c r="AF153" s="8">
         <v>10315.5</v>
@@ -17745,7 +17745,7 @@
         <v>45444</v>
       </c>
       <c r="B154" s="8">
-        <v>19728.900000000001</v>
+        <v>19722.099999999999</v>
       </c>
       <c r="C154" s="8">
         <v>12158</v>
@@ -17796,7 +17796,7 @@
         <v>0.2</v>
       </c>
       <c r="S154" s="8">
-        <v>7570.9</v>
+        <v>7564.1</v>
       </c>
       <c r="T154" s="8">
         <v>1710.7</v>
@@ -17811,28 +17811,28 @@
         <v>1486</v>
       </c>
       <c r="X154" s="8">
-        <v>3934.1</v>
+        <v>3926.5</v>
       </c>
       <c r="Y154" s="8">
         <v>232.4</v>
       </c>
       <c r="Z154" s="8">
-        <v>199.5</v>
+        <v>200.3</v>
       </c>
       <c r="AA154" s="8">
-        <v>3136.7</v>
+        <v>3139.1</v>
       </c>
       <c r="AB154" s="8">
         <v>3.9</v>
       </c>
       <c r="AC154" s="8">
-        <v>2969.6</v>
+        <v>2971.5</v>
       </c>
       <c r="AD154" s="8">
-        <v>163.19999999999999</v>
+        <v>163.80000000000001</v>
       </c>
       <c r="AE154" s="8">
-        <v>16592.2</v>
+        <v>16583</v>
       </c>
       <c r="AF154" s="8">
         <v>10568.2</v>
@@ -17846,7 +17846,7 @@
         <v>45536</v>
       </c>
       <c r="B155" s="8">
-        <v>20073</v>
+        <v>20068</v>
       </c>
       <c r="C155" s="8">
         <v>12218.9</v>
@@ -17882,7 +17882,7 @@
         <v>23.7</v>
       </c>
       <c r="N155" s="8">
-        <v>2.2999999999999998</v>
+        <v>2.4</v>
       </c>
       <c r="O155" s="8">
         <v>1</v>
@@ -17897,10 +17897,10 @@
         <v>0.2</v>
       </c>
       <c r="S155" s="8">
-        <v>7854</v>
+        <v>7849.1</v>
       </c>
       <c r="T155" s="8">
-        <v>1771.5</v>
+        <v>1771.4</v>
       </c>
       <c r="U155" s="8">
         <v>7</v>
@@ -17909,31 +17909,31 @@
         <v>1</v>
       </c>
       <c r="W155" s="8">
-        <v>1535.5</v>
+        <v>1535.4</v>
       </c>
       <c r="X155" s="8">
-        <v>4080.2</v>
+        <v>4073.3</v>
       </c>
       <c r="Y155" s="8">
         <v>239.1</v>
       </c>
       <c r="Z155" s="8">
-        <v>219.7</v>
+        <v>221.7</v>
       </c>
       <c r="AA155" s="8">
-        <v>3165.9</v>
+        <v>3167.9</v>
       </c>
       <c r="AB155" s="8">
         <v>3.8</v>
       </c>
       <c r="AC155" s="8">
-        <v>3000.2</v>
+        <v>3001.6</v>
       </c>
       <c r="AD155" s="8">
-        <v>162</v>
+        <v>162.5</v>
       </c>
       <c r="AE155" s="8">
-        <v>16907</v>
+        <v>16900.099999999999</v>
       </c>
       <c r="AF155" s="8">
         <v>10619.4</v>
@@ -17947,13 +17947,13 @@
         <v>45627</v>
       </c>
       <c r="B156" s="8">
-        <v>20504.599999999999</v>
+        <v>20499.599999999999</v>
       </c>
       <c r="C156" s="8">
-        <v>12485.8</v>
+        <v>12485.9</v>
       </c>
       <c r="D156" s="8">
-        <v>3940.6</v>
+        <v>3940.7</v>
       </c>
       <c r="E156" s="8">
         <v>3910.8</v>
@@ -17977,13 +17977,13 @@
         <v>11.8</v>
       </c>
       <c r="L156" s="8">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="M156" s="8">
         <v>23.8</v>
       </c>
       <c r="N156" s="8">
-        <v>5</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="O156" s="8">
         <v>1.1000000000000001</v>
@@ -17998,10 +17998,10 @@
         <v>0.2</v>
       </c>
       <c r="S156" s="8">
-        <v>8018.7</v>
+        <v>8013.7</v>
       </c>
       <c r="T156" s="8">
-        <v>1828.8</v>
+        <v>1828.7</v>
       </c>
       <c r="U156" s="8">
         <v>7.1</v>
@@ -18010,31 +18010,31 @@
         <v>1</v>
       </c>
       <c r="W156" s="8">
-        <v>1565.8</v>
+        <v>1565.7</v>
       </c>
       <c r="X156" s="8">
-        <v>4144.8</v>
+        <v>4136.8999999999996</v>
       </c>
       <c r="Y156" s="8">
         <v>234</v>
       </c>
       <c r="Z156" s="8">
-        <v>237.3</v>
+        <v>240.4</v>
       </c>
       <c r="AA156" s="8">
-        <v>3210.3</v>
+        <v>3215.5</v>
       </c>
       <c r="AB156" s="8">
         <v>3.7</v>
       </c>
       <c r="AC156" s="8">
-        <v>3045.9</v>
+        <v>3049.1</v>
       </c>
       <c r="AD156" s="8">
-        <v>160.6</v>
+        <v>162.80000000000001</v>
       </c>
       <c r="AE156" s="8">
-        <v>17294.3</v>
+        <v>17284.099999999999</v>
       </c>
       <c r="AF156" s="8">
         <v>10873.9</v>
@@ -18048,13 +18048,13 @@
         <v>45717</v>
       </c>
       <c r="B157" s="8">
-        <v>20655.400000000001</v>
+        <v>20651.3</v>
       </c>
       <c r="C157" s="8">
-        <v>12581</v>
+        <v>12581.1</v>
       </c>
       <c r="D157" s="8">
-        <v>3971.1</v>
+        <v>3971.3</v>
       </c>
       <c r="E157" s="8">
         <v>3940.2</v>
@@ -18078,13 +18078,13 @@
         <v>12.1</v>
       </c>
       <c r="L157" s="8">
-        <v>30.9</v>
+        <v>31.1</v>
       </c>
       <c r="M157" s="8">
         <v>24.3</v>
       </c>
       <c r="N157" s="8">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O157" s="8">
         <v>1.2</v>
@@ -18099,10 +18099,10 @@
         <v>0.2</v>
       </c>
       <c r="S157" s="8">
-        <v>8074.4</v>
+        <v>8070.2</v>
       </c>
       <c r="T157" s="8">
-        <v>1857.4</v>
+        <v>1857.1</v>
       </c>
       <c r="U157" s="8">
         <v>6.9</v>
@@ -18111,31 +18111,31 @@
         <v>0.9</v>
       </c>
       <c r="W157" s="8">
-        <v>1582.8</v>
+        <v>1582.6</v>
       </c>
       <c r="X157" s="8">
-        <v>4130.1000000000004</v>
+        <v>4122.3</v>
       </c>
       <c r="Y157" s="8">
-        <v>237.3</v>
+        <v>237.4</v>
       </c>
       <c r="Z157" s="8">
-        <v>259</v>
+        <v>262.89999999999998</v>
       </c>
       <c r="AA157" s="8">
-        <v>3250.2</v>
+        <v>3256.3</v>
       </c>
       <c r="AB157" s="8">
         <v>3.5</v>
       </c>
       <c r="AC157" s="8">
-        <v>3089.2</v>
+        <v>3092</v>
       </c>
       <c r="AD157" s="8">
-        <v>157.4</v>
+        <v>160.80000000000001</v>
       </c>
       <c r="AE157" s="8">
-        <v>17405.2</v>
+        <v>17395</v>
       </c>
       <c r="AF157" s="8">
         <v>10960</v>
@@ -18149,13 +18149,13 @@
         <v>45809</v>
       </c>
       <c r="B158" s="8">
-        <v>21157.8</v>
+        <v>21236.7</v>
       </c>
       <c r="C158" s="8">
-        <v>12780.4</v>
+        <v>12862.5</v>
       </c>
       <c r="D158" s="8">
-        <v>3998.1</v>
+        <v>3998.2</v>
       </c>
       <c r="E158" s="8">
         <v>3969</v>
@@ -18179,31 +18179,31 @@
         <v>12.4</v>
       </c>
       <c r="L158" s="8">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="M158" s="8">
         <v>24</v>
       </c>
       <c r="N158" s="8">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O158" s="8">
         <v>1.2</v>
       </c>
       <c r="P158" s="8">
-        <v>8782.4</v>
+        <v>8864.2999999999993</v>
       </c>
       <c r="Q158" s="8">
-        <v>8782.2000000000007</v>
+        <v>8864.1</v>
       </c>
       <c r="R158" s="8">
         <v>0.2</v>
       </c>
       <c r="S158" s="8">
-        <v>8377.2999999999993</v>
+        <v>8374.1</v>
       </c>
       <c r="T158" s="8">
-        <v>1863.4</v>
+        <v>1863</v>
       </c>
       <c r="U158" s="8">
         <v>6.9</v>
@@ -18212,34 +18212,34 @@
         <v>0.8</v>
       </c>
       <c r="W158" s="8">
-        <v>1641.8</v>
+        <v>1641.6</v>
       </c>
       <c r="X158" s="8">
-        <v>4337.5</v>
+        <v>4329.7</v>
       </c>
       <c r="Y158" s="8">
-        <v>244.8</v>
+        <v>244.9</v>
       </c>
       <c r="Z158" s="8">
-        <v>282.2</v>
+        <v>287.3</v>
       </c>
       <c r="AA158" s="8">
-        <v>3308.3</v>
+        <v>3316.4</v>
       </c>
       <c r="AB158" s="8">
         <v>3.4</v>
       </c>
       <c r="AC158" s="8">
-        <v>3152.4</v>
+        <v>3155.9</v>
       </c>
       <c r="AD158" s="8">
-        <v>152.5</v>
+        <v>157.1</v>
       </c>
       <c r="AE158" s="8">
-        <v>17849.400000000001</v>
+        <v>17920.3</v>
       </c>
       <c r="AF158" s="8">
-        <v>11154.1</v>
+        <v>11236</v>
       </c>
       <c r="AG158" s="8">
         <v>572.29999999999995</v>
@@ -18250,13 +18250,13 @@
         <v>45901</v>
       </c>
       <c r="B159" s="8">
-        <v>21737.599999999999</v>
+        <v>21793.1</v>
       </c>
       <c r="C159" s="8">
-        <v>13089.5</v>
+        <v>13138.2</v>
       </c>
       <c r="D159" s="8">
-        <v>4025.4</v>
+        <v>4025.7</v>
       </c>
       <c r="E159" s="8">
         <v>3998.4</v>
@@ -18280,31 +18280,31 @@
         <v>12.7</v>
       </c>
       <c r="L159" s="8">
-        <v>27</v>
+        <v>27.3</v>
       </c>
       <c r="M159" s="8">
         <v>24.1</v>
       </c>
       <c r="N159" s="8">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="O159" s="8">
         <v>1.3</v>
       </c>
       <c r="P159" s="8">
-        <v>9064.1</v>
+        <v>9112.5</v>
       </c>
       <c r="Q159" s="8">
-        <v>9063.9</v>
+        <v>9112.2999999999993</v>
       </c>
       <c r="R159" s="8">
         <v>0.2</v>
       </c>
       <c r="S159" s="8">
-        <v>8648.1</v>
+        <v>8654.9</v>
       </c>
       <c r="T159" s="8">
-        <v>1927</v>
+        <v>1926.8</v>
       </c>
       <c r="U159" s="8">
         <v>7.1</v>
@@ -18313,37 +18313,239 @@
         <v>0.7</v>
       </c>
       <c r="W159" s="8">
-        <v>1680</v>
+        <v>1679.5</v>
       </c>
       <c r="X159" s="8">
-        <v>4497.7</v>
+        <v>4493.8999999999996</v>
       </c>
       <c r="Y159" s="8">
-        <v>247.7</v>
+        <v>251.5</v>
       </c>
       <c r="Z159" s="8">
-        <v>287.8</v>
+        <v>295.3</v>
       </c>
       <c r="AA159" s="8">
-        <v>3336.9</v>
+        <v>3344.8</v>
       </c>
       <c r="AB159" s="8">
         <v>3.2</v>
       </c>
       <c r="AC159" s="8">
-        <v>3181.1</v>
+        <v>3186.1</v>
       </c>
       <c r="AD159" s="8">
-        <v>152.6</v>
+        <v>155.5</v>
       </c>
       <c r="AE159" s="8">
-        <v>18400.7</v>
+        <v>18448.3</v>
       </c>
       <c r="AF159" s="8">
-        <v>11457.8</v>
+        <v>11506.2</v>
       </c>
       <c r="AG159" s="8">
         <v>575.79999999999995</v>
+      </c>
+    </row>
+    <row r="160" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A160" s="9">
+        <v>45992</v>
+      </c>
+      <c r="B160" s="8">
+        <v>22394.799999999999</v>
+      </c>
+      <c r="C160" s="8">
+        <v>13609.2</v>
+      </c>
+      <c r="D160" s="8">
+        <v>4060.8</v>
+      </c>
+      <c r="E160" s="8">
+        <v>4029.4</v>
+      </c>
+      <c r="F160" s="8">
+        <v>3129</v>
+      </c>
+      <c r="G160" s="8">
+        <v>350.4</v>
+      </c>
+      <c r="H160" s="8">
+        <v>322.5</v>
+      </c>
+      <c r="I160" s="8">
+        <v>181</v>
+      </c>
+      <c r="J160" s="8">
+        <v>33.6</v>
+      </c>
+      <c r="K160" s="8">
+        <v>12.9</v>
+      </c>
+      <c r="L160" s="8">
+        <v>31.4</v>
+      </c>
+      <c r="M160" s="8">
+        <v>24.3</v>
+      </c>
+      <c r="N160" s="8">
+        <v>5.7</v>
+      </c>
+      <c r="O160" s="8">
+        <v>1.4</v>
+      </c>
+      <c r="P160" s="8">
+        <v>9548.4</v>
+      </c>
+      <c r="Q160" s="8">
+        <v>9548.2000000000007</v>
+      </c>
+      <c r="R160" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="S160" s="8">
+        <v>8785.6</v>
+      </c>
+      <c r="T160" s="8">
+        <v>1982.2</v>
+      </c>
+      <c r="U160" s="8">
+        <v>7.3</v>
+      </c>
+      <c r="V160" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="W160" s="8">
+        <v>1699.5</v>
+      </c>
+      <c r="X160" s="8">
+        <v>4543.2</v>
+      </c>
+      <c r="Y160" s="8">
+        <v>254.4</v>
+      </c>
+      <c r="Z160" s="8">
+        <v>298.39999999999998</v>
+      </c>
+      <c r="AA160" s="8">
+        <v>3407.9</v>
+      </c>
+      <c r="AB160" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="AC160" s="8">
+        <v>3250.1</v>
+      </c>
+      <c r="AD160" s="8">
+        <v>154.69999999999999</v>
+      </c>
+      <c r="AE160" s="8">
+        <v>18987</v>
+      </c>
+      <c r="AF160" s="8">
+        <v>11964.7</v>
+      </c>
+      <c r="AG160" s="8">
+        <v>579.29999999999995</v>
+      </c>
+    </row>
+    <row r="161" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A161" s="9">
+        <v>46082</v>
+      </c>
+      <c r="B161" s="8">
+        <v>22665.7</v>
+      </c>
+      <c r="C161" s="8">
+        <v>13922</v>
+      </c>
+      <c r="D161" s="8">
+        <v>4094.9</v>
+      </c>
+      <c r="E161" s="8">
+        <v>4062.5</v>
+      </c>
+      <c r="F161" s="8">
+        <v>3156</v>
+      </c>
+      <c r="G161" s="8">
+        <v>353.8</v>
+      </c>
+      <c r="H161" s="8">
+        <v>324.7</v>
+      </c>
+      <c r="I161" s="8">
+        <v>181.6</v>
+      </c>
+      <c r="J161" s="8">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="K161" s="8">
+        <v>13.2</v>
+      </c>
+      <c r="L161" s="8">
+        <v>32.4</v>
+      </c>
+      <c r="M161" s="8">
+        <v>24.7</v>
+      </c>
+      <c r="N161" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="O161" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="P161" s="8">
+        <v>9827.1</v>
+      </c>
+      <c r="Q161" s="8">
+        <v>9827</v>
+      </c>
+      <c r="R161" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="S161" s="8">
+        <v>8743.6</v>
+      </c>
+      <c r="T161" s="8">
+        <v>2003.3</v>
+      </c>
+      <c r="U161" s="8">
+        <v>7.6</v>
+      </c>
+      <c r="V161" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="W161" s="8">
+        <v>1712</v>
+      </c>
+      <c r="X161" s="8">
+        <v>4470.3</v>
+      </c>
+      <c r="Y161" s="8">
+        <v>246.8</v>
+      </c>
+      <c r="Z161" s="8">
+        <v>303</v>
+      </c>
+      <c r="AA161" s="8">
+        <v>3453.8</v>
+      </c>
+      <c r="AB161" s="8">
+        <v>3</v>
+      </c>
+      <c r="AC161" s="8">
+        <v>3296.6</v>
+      </c>
+      <c r="AD161" s="8">
+        <v>154.19999999999999</v>
+      </c>
+      <c r="AE161" s="8">
+        <v>19211.900000000001</v>
+      </c>
+      <c r="AF161" s="8">
+        <v>12266.8</v>
+      </c>
+      <c r="AG161" s="8">
+        <v>583</v>
       </c>
     </row>
   </sheetData>
